--- a/data/content-review-batches/16_rows_151-160.xlsx
+++ b/data/content-review-batches/16_rows_151-160.xlsx
@@ -480,20 +480,18 @@
         <x:is>
           <x:t xml:space="preserve">אופן הכנה:
 נטבול את הביסקוויטים בחלב למספר שניות ונסדר שכבה ראשונה בתבנית
-הכנת הקרם:
-נקציף את השמנת עם הסוכר במשך שתי דקות
+הכנת הקרם: נקציף את השמנת עם הסוכר במשך שתי דקות
 לאחר מכן נוסיף את החלב את האינסטנט פודינג ואת מחית הפיסטוק
 נמשיך להקציף עד לקבלת קצפת יציבה ואחידה
 נמרח מעל שכבת הביסקוויטים שכבה של קרם
 נסדר שכבת ביסקוויטים נוספת ומעליה שכבה נוספת של קרם
 בסך הכול שתי שכבות ביסקוויטים ושתי שכבות קרם
 נכניס את העוגה למקרר בזמן שמכינים את הגנאש
-הכנת הגנאש:
-נמיס את השוקולד הלבן והשמנת במיקרוגל בפולסים של חצי דקה
+הכנת הגנאש: נמיס את השוקולד הלבן והשמנת במיקרוגל בפולסים של חצי דקה
 נערבב היטב עד לקבלת מרקם חלק
 נוסיף את מחית הפיסטוק ונערבב לאיחוד
 נוציא את העוגה מהמקרר ונצפה אותה בגנאש בצורה אחידה
-•ליצירת ציורים של לבבות נשמור קצת מהגנאש לפני הוספת המחית פיסטוק ונצייר כמו בסרטון 
+ליצירת ציורים של לבבות נשמור קצת מהגנאש לפני הוספת המחית פיסטוק ונצייר כמו בסרטון
 נחזיר למקרר ללילה שלם להתייצבות
 זה מאתגר לחכות אבל לגמרי שווה את זה 🫣
 למחרת חותכים מגישים ובתאבון ❤️❤️❤</x:t>
@@ -742,8 +740,7 @@
 את ביסקוויטי הקרמבו חותכים לחתיכות קטנות ושומרים בצד
 מעבירים את הקרם לשקית זילוף ומזלפים את הקרם בין הקרמבואים
 מכניסים את התבנית למקרר בזמן שמכינים את הגנאש
-להכנת הגנאש
-ממיסים את השוקולד המריר, שוקולד החלב והשמנת המתוקה במיקרוגל בפולסים של חצי דקה תוך ערבוב בין חימום לחימום עד לקבלת מרקם חלק ואחיד
+להכנת הגנאש: ממיסים את השוקולד המריר, שוקולד החלב והשמנת המתוקה במיקרוגל בפולסים של חצי דקה תוך ערבוב בין חימום לחימום עד לקבלת מרקם חלק ואחיד
 יוצקים את הגנאש מעל העוגה
 מפזרים מעל את חתיכות ביסקוויטי הקרמבו ששמרנו בצד
 מכניסים את העוגה למקרר להתייצבות מלאה למשך לילה
@@ -927,8 +924,7 @@
 מורחים חצי מכמות הקרם
 מסדרים שכבה נוספת של ביסקוויטים ומעליה מורחים את יתרת הקרם
 מכניסים את העוגה למקרר
-להכנת הגנאש:
-מחממים את השמנת המתוקה במיקרוגל יחד עם הקפה
+להכנת הגנאש: מחממים את השמנת המתוקה במיקרוגל יחד עם הקפה
 מערבבים עד שכל גרגירי הקפה נמסים
 מוסיפים את השוקולד הלבן וממיסים הכול יחד במיקרוגל בפולסים של חצי דקה
 מוזגים את הגנאש מעל העוגה
@@ -1097,12 +1093,12 @@
       </x:c>
       <x:c r="M10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">קל</x:t>
         </x:is>
       </x:c>
       <x:c r="N10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">30</x:t>
         </x:is>
       </x:c>
     </x:row>
